--- a/panchang-data/Ludhiana2026.xlsx
+++ b/panchang-data/Ludhiana2026.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5388">
   <si>
     <t>दिनाङ्क</t>
   </si>
@@ -16189,6 +16189,9 @@
   </si>
   <si>
     <t>121°05'01.53</t>
+  </si>
+  <si>
+    <t>ज्येष्ठ अधिक</t>
   </si>
 </sst>
 </file>
@@ -16678,7 +16681,7 @@
         <v>46023</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>29</v>
@@ -16764,7 +16767,7 @@
         <v>46024</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>51</v>
@@ -16850,7 +16853,7 @@
         <v>46025</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>70</v>
@@ -16936,7 +16939,7 @@
         <v>46026</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>90</v>
@@ -17022,7 +17025,7 @@
         <v>46027</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>108</v>
@@ -17108,7 +17111,7 @@
         <v>46028</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>126</v>
@@ -17194,7 +17197,7 @@
         <v>46029</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>144</v>
@@ -17280,7 +17283,7 @@
         <v>46030</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>29</v>
@@ -17366,7 +17369,7 @@
         <v>46031</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>51</v>
@@ -17452,7 +17455,7 @@
         <v>46032</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>70</v>
@@ -17538,7 +17541,7 @@
         <v>46033</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>90</v>
@@ -17624,7 +17627,7 @@
         <v>46034</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>108</v>
@@ -17710,7 +17713,7 @@
         <v>46035</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>126</v>
@@ -17796,7 +17799,7 @@
         <v>46036</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>144</v>
@@ -17882,7 +17885,7 @@
         <v>46037</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>29</v>
@@ -17968,7 +17971,7 @@
         <v>46038</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>51</v>
@@ -18054,7 +18057,7 @@
         <v>46039</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>70</v>
@@ -18140,7 +18143,7 @@
         <v>46040</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>90</v>
@@ -18226,7 +18229,7 @@
         <v>46041</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>108</v>
@@ -18312,7 +18315,7 @@
         <v>46042</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>126</v>
@@ -18398,7 +18401,7 @@
         <v>46043</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>144</v>
@@ -18484,7 +18487,7 @@
         <v>46044</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>29</v>
@@ -18570,7 +18573,7 @@
         <v>46045</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>51</v>
@@ -18656,7 +18659,7 @@
         <v>46046</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>70</v>
@@ -18742,7 +18745,7 @@
         <v>46047</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>90</v>
@@ -18828,7 +18831,7 @@
         <v>46048</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>108</v>
@@ -18914,7 +18917,7 @@
         <v>46049</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>126</v>
@@ -19000,7 +19003,7 @@
         <v>46050</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>144</v>
@@ -19086,7 +19089,7 @@
         <v>46051</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>29</v>
@@ -19172,7 +19175,7 @@
         <v>46052</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>51</v>
@@ -19258,7 +19261,7 @@
         <v>46053</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>70</v>
@@ -19344,7 +19347,7 @@
         <v>46054</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>90</v>
@@ -19430,7 +19433,7 @@
         <v>46055</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>108</v>
@@ -19516,7 +19519,7 @@
         <v>46056</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>126</v>
@@ -19602,7 +19605,7 @@
         <v>46057</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>144</v>
@@ -19688,7 +19691,7 @@
         <v>46058</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>29</v>
@@ -19774,7 +19777,7 @@
         <v>46059</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>51</v>
@@ -19860,7 +19863,7 @@
         <v>46060</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>70</v>
@@ -19946,7 +19949,7 @@
         <v>46061</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>90</v>
@@ -20032,7 +20035,7 @@
         <v>46062</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>108</v>
@@ -20118,7 +20121,7 @@
         <v>46063</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>126</v>
@@ -20204,7 +20207,7 @@
         <v>46064</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>144</v>
@@ -20290,7 +20293,7 @@
         <v>46065</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>29</v>
@@ -20376,7 +20379,7 @@
         <v>46066</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>51</v>
@@ -20462,7 +20465,7 @@
         <v>46067</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>70</v>
@@ -20548,7 +20551,7 @@
         <v>46068</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>90</v>
@@ -20634,7 +20637,7 @@
         <v>46069</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>108</v>
@@ -20720,7 +20723,7 @@
         <v>46070</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>126</v>
@@ -20806,7 +20809,7 @@
         <v>46071</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>144</v>
@@ -20892,7 +20895,7 @@
         <v>46072</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>29</v>
@@ -20978,7 +20981,7 @@
         <v>46073</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>51</v>
@@ -21064,7 +21067,7 @@
         <v>46074</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>70</v>
@@ -21150,7 +21153,7 @@
         <v>46075</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>90</v>
@@ -21236,7 +21239,7 @@
         <v>46076</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>108</v>
@@ -21322,7 +21325,7 @@
         <v>46077</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>126</v>
@@ -21408,7 +21411,7 @@
         <v>46078</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>144</v>
@@ -21494,7 +21497,7 @@
         <v>46079</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>29</v>
@@ -21580,7 +21583,7 @@
         <v>46080</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>51</v>
@@ -21666,7 +21669,7 @@
         <v>46081</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>70</v>
@@ -21752,7 +21755,7 @@
         <v>46082</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>90</v>
@@ -21838,7 +21841,7 @@
         <v>46083</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>108</v>
@@ -21924,7 +21927,7 @@
         <v>46084</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>126</v>
@@ -22010,7 +22013,7 @@
         <v>46085</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>144</v>
@@ -22096,7 +22099,7 @@
         <v>46086</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>29</v>
@@ -22182,7 +22185,7 @@
         <v>46087</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>51</v>
@@ -22268,7 +22271,7 @@
         <v>46088</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>70</v>
@@ -22354,7 +22357,7 @@
         <v>46089</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>90</v>
@@ -22440,7 +22443,7 @@
         <v>46090</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>108</v>
@@ -22526,7 +22529,7 @@
         <v>46091</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>126</v>
@@ -22612,7 +22615,7 @@
         <v>46092</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>144</v>
@@ -22698,7 +22701,7 @@
         <v>46093</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>29</v>
@@ -22784,7 +22787,7 @@
         <v>46094</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>51</v>
@@ -22870,7 +22873,7 @@
         <v>46095</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>70</v>
@@ -22956,7 +22959,7 @@
         <v>46096</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>90</v>
@@ -23042,7 +23045,7 @@
         <v>46097</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>108</v>
@@ -23128,7 +23131,7 @@
         <v>46098</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>126</v>
@@ -23214,7 +23217,7 @@
         <v>46099</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>144</v>
@@ -23300,7 +23303,7 @@
         <v>46100</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>29</v>
@@ -23386,7 +23389,7 @@
         <v>46101</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>51</v>
@@ -23472,7 +23475,7 @@
         <v>46102</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>70</v>
@@ -23558,7 +23561,7 @@
         <v>46103</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>90</v>
@@ -23644,7 +23647,7 @@
         <v>46104</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>108</v>
@@ -23730,7 +23733,7 @@
         <v>46105</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>126</v>
@@ -23816,7 +23819,7 @@
         <v>46106</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>144</v>
@@ -23902,7 +23905,7 @@
         <v>46107</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>29</v>
@@ -23988,7 +23991,7 @@
         <v>46108</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>51</v>
@@ -24074,7 +24077,7 @@
         <v>46109</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>70</v>
@@ -24160,7 +24163,7 @@
         <v>46110</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>90</v>
@@ -24246,7 +24249,7 @@
         <v>46111</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>108</v>
@@ -24332,7 +24335,7 @@
         <v>46112</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>126</v>
@@ -24418,7 +24421,7 @@
         <v>46113</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>144</v>
@@ -24504,7 +24507,7 @@
         <v>46114</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>29</v>
@@ -24590,7 +24593,7 @@
         <v>46115</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>1450</v>
+        <v>1872</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>51</v>
@@ -24676,7 +24679,7 @@
         <v>46116</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>1450</v>
+        <v>1872</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>70</v>
@@ -24762,7 +24765,7 @@
         <v>46117</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>1450</v>
+        <v>1872</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>90</v>
@@ -24848,7 +24851,7 @@
         <v>46118</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>1450</v>
+        <v>1872</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>108</v>
@@ -24934,7 +24937,7 @@
         <v>46119</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>1450</v>
+        <v>1872</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>126</v>
@@ -25020,7 +25023,7 @@
         <v>46120</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>1450</v>
+        <v>1872</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>144</v>
@@ -25106,7 +25109,7 @@
         <v>46121</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>1450</v>
+        <v>1872</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>29</v>
@@ -25192,7 +25195,7 @@
         <v>46122</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>1450</v>
+        <v>1872</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>51</v>
@@ -25278,7 +25281,7 @@
         <v>46123</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>1450</v>
+        <v>1872</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>70</v>
@@ -25364,7 +25367,7 @@
         <v>46124</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>1450</v>
+        <v>1872</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>90</v>
@@ -25450,7 +25453,7 @@
         <v>46125</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>1450</v>
+        <v>1872</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>108</v>
@@ -25536,7 +25539,7 @@
         <v>46126</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>1450</v>
+        <v>1872</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>126</v>
@@ -25622,7 +25625,7 @@
         <v>46127</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>1450</v>
+        <v>1872</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>144</v>
@@ -25708,7 +25711,7 @@
         <v>46128</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>1450</v>
+        <v>1872</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>29</v>
@@ -25794,7 +25797,7 @@
         <v>46129</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>1450</v>
+        <v>1872</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>51</v>
@@ -25880,7 +25883,7 @@
         <v>46130</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>1450</v>
+        <v>1872</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>70</v>
@@ -25966,7 +25969,7 @@
         <v>46131</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>1450</v>
+        <v>1872</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>90</v>
@@ -26052,7 +26055,7 @@
         <v>46132</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>1450</v>
+        <v>1872</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>108</v>
@@ -26138,7 +26141,7 @@
         <v>46133</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>1450</v>
+        <v>1872</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>126</v>
@@ -26224,7 +26227,7 @@
         <v>46134</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>1450</v>
+        <v>1872</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>144</v>
@@ -26310,7 +26313,7 @@
         <v>46135</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>1450</v>
+        <v>1872</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>29</v>
@@ -26396,7 +26399,7 @@
         <v>46136</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>1450</v>
+        <v>1872</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>51</v>
@@ -26482,7 +26485,7 @@
         <v>46137</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>1450</v>
+        <v>1872</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>70</v>
@@ -26568,7 +26571,7 @@
         <v>46138</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>1450</v>
+        <v>1872</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>90</v>
@@ -26654,7 +26657,7 @@
         <v>46139</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>1450</v>
+        <v>1872</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>108</v>
@@ -26740,7 +26743,7 @@
         <v>46140</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>1450</v>
+        <v>1872</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>126</v>
@@ -26826,7 +26829,7 @@
         <v>46141</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>1450</v>
+        <v>1872</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>144</v>
@@ -26912,7 +26915,7 @@
         <v>46142</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>1450</v>
+        <v>1872</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>29</v>
@@ -26998,7 +27001,7 @@
         <v>46143</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>1450</v>
+        <v>1872</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>51</v>
@@ -27084,7 +27087,7 @@
         <v>46144</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>1872</v>
+        <v>2309</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>70</v>
@@ -27170,7 +27173,7 @@
         <v>46145</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>1872</v>
+        <v>2309</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>90</v>
@@ -27256,7 +27259,7 @@
         <v>46146</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>1872</v>
+        <v>2309</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>108</v>
@@ -27342,7 +27345,7 @@
         <v>46147</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>1872</v>
+        <v>2309</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>126</v>
@@ -27428,7 +27431,7 @@
         <v>46148</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>1872</v>
+        <v>2309</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>144</v>
@@ -27514,7 +27517,7 @@
         <v>46149</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>1872</v>
+        <v>2309</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>29</v>
@@ -27600,7 +27603,7 @@
         <v>46150</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>1872</v>
+        <v>2309</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>51</v>
@@ -27686,7 +27689,7 @@
         <v>46151</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>1872</v>
+        <v>2309</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>70</v>
@@ -27772,7 +27775,7 @@
         <v>46152</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>1872</v>
+        <v>2309</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>90</v>
@@ -27858,7 +27861,7 @@
         <v>46153</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>1872</v>
+        <v>2309</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>108</v>
@@ -27944,7 +27947,7 @@
         <v>46154</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>1872</v>
+        <v>2309</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>126</v>
@@ -28030,7 +28033,7 @@
         <v>46155</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>1872</v>
+        <v>2309</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>144</v>
@@ -28116,7 +28119,7 @@
         <v>46156</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>1872</v>
+        <v>2309</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>29</v>
@@ -28202,7 +28205,7 @@
         <v>46157</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>1872</v>
+        <v>2309</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>51</v>
@@ -28288,7 +28291,7 @@
         <v>46158</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>1872</v>
+        <v>2309</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>70</v>
@@ -28374,7 +28377,7 @@
         <v>46159</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>1872</v>
+        <v>5387</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>90</v>
@@ -28460,7 +28463,7 @@
         <v>46160</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>1872</v>
+        <v>5387</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>108</v>
@@ -28546,7 +28549,7 @@
         <v>46161</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>1872</v>
+        <v>5387</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>126</v>
@@ -28632,7 +28635,7 @@
         <v>46162</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>1872</v>
+        <v>5387</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>144</v>
@@ -28718,7 +28721,7 @@
         <v>46163</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>1872</v>
+        <v>5387</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>29</v>
@@ -28804,7 +28807,7 @@
         <v>46164</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>1872</v>
+        <v>5387</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>51</v>
@@ -28890,7 +28893,7 @@
         <v>46165</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>1872</v>
+        <v>5387</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>70</v>
@@ -28976,7 +28979,7 @@
         <v>46166</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>1872</v>
+        <v>5387</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>90</v>
@@ -29062,7 +29065,7 @@
         <v>46167</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>1872</v>
+        <v>5387</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>108</v>
@@ -29148,7 +29151,7 @@
         <v>46168</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>1872</v>
+        <v>5387</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>126</v>
@@ -29234,7 +29237,7 @@
         <v>46169</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>1872</v>
+        <v>5387</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>144</v>
@@ -29320,7 +29323,7 @@
         <v>46170</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>1872</v>
+        <v>5387</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>29</v>
@@ -29406,7 +29409,7 @@
         <v>46171</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>1872</v>
+        <v>5387</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>51</v>
@@ -29492,7 +29495,7 @@
         <v>46172</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>1872</v>
+        <v>5387</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>70</v>
@@ -29578,7 +29581,7 @@
         <v>46173</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>1872</v>
+        <v>5387</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>90</v>
@@ -29664,7 +29667,7 @@
         <v>46174</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>2309</v>
+        <v>5387</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>108</v>
@@ -29750,7 +29753,7 @@
         <v>46175</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>2309</v>
+        <v>5387</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>126</v>
@@ -29836,7 +29839,7 @@
         <v>46176</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>2309</v>
+        <v>5387</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>144</v>
@@ -29922,7 +29925,7 @@
         <v>46177</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>2309</v>
+        <v>5387</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>29</v>
@@ -30008,7 +30011,7 @@
         <v>46178</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>2309</v>
+        <v>5387</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>51</v>
@@ -30094,7 +30097,7 @@
         <v>46179</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>2309</v>
+        <v>5387</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>70</v>
@@ -30180,7 +30183,7 @@
         <v>46180</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>2309</v>
+        <v>5387</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>90</v>
@@ -30266,7 +30269,7 @@
         <v>46181</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>2309</v>
+        <v>5387</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>108</v>
@@ -30352,7 +30355,7 @@
         <v>46182</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>2309</v>
+        <v>5387</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>126</v>
@@ -30438,7 +30441,7 @@
         <v>46183</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>2309</v>
+        <v>5387</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>144</v>
@@ -30524,7 +30527,7 @@
         <v>46184</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>2309</v>
+        <v>5387</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>29</v>
@@ -30610,7 +30613,7 @@
         <v>46185</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>2309</v>
+        <v>5387</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>51</v>
@@ -30696,7 +30699,7 @@
         <v>46186</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>2309</v>
+        <v>5387</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>70</v>
@@ -30782,7 +30785,7 @@
         <v>46187</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>2309</v>
+        <v>5387</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>90</v>
@@ -30868,7 +30871,7 @@
         <v>46188</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>2309</v>
+        <v>5387</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>108</v>
